--- a/mapping/npc_account_from_contact.xlsx
+++ b/mapping/npc_account_from_contact.xlsx
@@ -443,6 +443,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -2671,7 +2672,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Exact name match (normalized). Only 100.0% populated, and every populated row has the same value ("005fj00000J30tNAAR") -- no differentiating information, likely not worth migrating.</t>
+          <t>Exact name match (normalized). Only 100.0% populated, and every populated row has the same value ("&lt;SAMPLE_ID_REDACTED&gt;") -- no differentiating information, likely not worth migrating.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -2761,7 +2762,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>No confident match found -- needs manual review. Also: Only 100.0% populated, and every populated row has the same value ("005fj00000J30tNAAR") -- no differentiating information, likely not worth migrating.</t>
+          <t>No confident match found -- needs manual review. Also: Only 100.0% populated, and every populated row has the same value ("&lt;SAMPLE_ID_REDACTED&gt;") -- no differentiating information, likely not worth migrating.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -2831,7 +2832,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>No confident match found -- needs manual review. Also: Only 100.0% populated, and every populated row has the same value ("005fj00000J30tNAAR") -- no differentiating information, likely not worth migrating.</t>
+          <t>No confident match found -- needs manual review. Also: Only 100.0% populated, and every populated row has the same value ("&lt;SAMPLE_ID_REDACTED&gt;") -- no differentiating information, likely not worth migrating.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
